--- a/docs/iClosed-Security-Status.xlsx
+++ b/docs/iClosed-Security-Status.xlsx
@@ -181,7 +181,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-005</t>
+          <t xml:space="preserve">SEC-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -191,7 +191,7 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="3">
@@ -201,24 +201,24 @@
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Blob URL allow-list is hostname-based</t>
+          <t xml:space="preserve">Webhook HMAC signatures</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">new URL().hostname check</t>
+          <t xml:space="preserve">activate-deal auto-enforces when secret set; fail-open if missing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Set SERVICE_WEBHOOK_SECRET (same) in both Vercel projects + redeploy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-006</t>
+          <t xml:space="preserve">SEC-004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -238,24 +238,24 @@
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Impersonation step-up + notify + audit</t>
+          <t xml:space="preserve">Per-deal ownership (IDOR)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Admin re-enters password; customer emailed; audited</t>
+          <t xml:space="preserve">'All admins see all' kept as intended</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optional: IMPERSONATE_NOTIFY_CUSTOMER=false</t>
+          <t xml:space="preserve">Accepted decision: all admins see all deals (documented in CLAUDE.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-008</t>
+          <t xml:space="preserve">SEC-005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -275,24 +275,24 @@
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Invitation token consumption cap (max 10)</t>
+          <t xml:space="preserve">Blob URL allow-list is hostname-based</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+ migration</t>
+          <t xml:space="preserve">new URL().hostname check</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Run 2026-07-23-invitation-token-consumption-cap.sql</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-009</t>
+          <t xml:space="preserve">SEC-006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -312,24 +312,24 @@
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email template injection fixed</t>
+          <t xml:space="preserve">Impersonation step-up + notify + audit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Single-pass + HTML-escape renderer; 7/7 tests</t>
+          <t xml:space="preserve">Admin re-enters password; customer emailed; audited</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Optional: IMPERSONATE_NOTIFY_CUSTOMER=false</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-010</t>
+          <t xml:space="preserve">SEC-007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -349,24 +349,24 @@
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security headers</t>
+          <t xml:space="preserve">Password-reset rate limit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5 enforced; CSP report-only</t>
+          <t xml:space="preserve">Rate-limited via Supabase (no Redis)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Flip CSP to enforcing after console check</t>
+          <t xml:space="preserve">Run 2026-07-23-rate-limits.sql</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-012</t>
+          <t xml:space="preserve">SEC-008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -376,7 +376,7 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="3">
@@ -386,24 +386,24 @@
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Don't leak internal errors</t>
+          <t xml:space="preserve">Invitation token consumption cap (max 10)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Public routes fixed; admin-detail accepted (documented)</t>
+          <t xml:space="preserve">+ migration</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 2026-07-23-invitation-token-consumption-cap.sql</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-013</t>
+          <t xml:space="preserve">SEC-009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -413,7 +413,7 @@
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="3">
@@ -423,12 +423,12 @@
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UUID validation before .or() (deal+lead)</t>
+          <t xml:space="preserve">Email template injection fixed</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Guards string-interpolated filters</t>
+          <t xml:space="preserve">Single-pass + HTML-escape renderer; 7/7 tests</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="2">
@@ -440,7 +440,7 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-014</t>
+          <t xml:space="preserve">SEC-010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -450,7 +450,7 @@
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="3">
@@ -460,24 +460,24 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Removed verbose ID logging</t>
+          <t xml:space="preserve">Security headers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">task-responses diagnostics removed</t>
+          <t xml:space="preserve">5 enforced; CSP report-only</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Flip CSP to enforcing after console check</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-016</t>
+          <t xml:space="preserve">SEC-011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -487,7 +487,7 @@
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="3">
@@ -497,24 +497,24 @@
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secret-scanning CI (gitleaks)</t>
+          <t xml:space="preserve">Gemini per-user rate limit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rate-limited via Supabase (no Redis)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">.github workflow — enable Actions on GitHub</t>
+          <t xml:space="preserve">Run 2026-07-23-rate-limits.sql</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-017</t>
+          <t xml:space="preserve">SEC-012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -534,12 +534,12 @@
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Explicit CORS-deny on webhooks</t>
+          <t xml:space="preserve">Don't leak internal errors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server-to-server only</t>
+          <t xml:space="preserve">Public routes fixed; admin-detail accepted (documented)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="2">
@@ -551,7 +551,7 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-019</t>
+          <t xml:space="preserve">SEC-013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -571,24 +571,24 @@
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Dependabot config</t>
+          <t xml:space="preserve">UUID validation before .or() (deal+lead)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Guards string-interpolated filters</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">.github/dependabot.yml — enable on GitHub</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-020</t>
+          <t xml:space="preserve">SEC-014</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -608,12 +608,12 @@
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">server-only guard on supabaseAdmin</t>
+          <t xml:space="preserve">Removed verbose ID logging</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Throws if loaded in browser</t>
+          <t xml:space="preserve">task-responses diagnostics removed</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="2">
@@ -625,7 +625,7 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-022</t>
+          <t xml:space="preserve">SEC-016</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -645,24 +645,24 @@
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Recipient emails masked in logs</t>
+          <t xml:space="preserve">Secret-scanning CI (gitleaks)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+ PII subject dropped</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">.github workflow — enable Actions on GitHub</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-024</t>
+          <t xml:space="preserve">SEC-017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -682,12 +682,12 @@
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload token 2-min TTL</t>
+          <t xml:space="preserve">Explicit CORS-deny on webhooks</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">validUntil added</t>
+          <t xml:space="preserve">Server-to-server only</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-025</t>
+          <t xml:space="preserve">SEC-019</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -719,24 +719,24 @@
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">backfill-shared-tasks behind admin gate</t>
+          <t xml:space="preserve">Dependabot config</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">via middleware</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">.github/dependabot.yml — enable on GitHub</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-026</t>
+          <t xml:space="preserve">SEC-020</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -756,24 +756,24 @@
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">audit_logs table + recordAudit</t>
+          <t xml:space="preserve">server-only guard on supabaseAdmin</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">+ migration; wired impersonate/deletes</t>
+          <t xml:space="preserve">Throws if loaded in browser</t>
         </is>
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Run 2026-07-23-audit-logs.sql</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-027</t>
+          <t xml:space="preserve">SEC-022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -793,12 +793,12 @@
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Key-rotation runbook</t>
+          <t xml:space="preserve">Recipient emails masked in logs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">docs/key-rotation.md</t>
+          <t xml:space="preserve">+ PII subject dropped</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="2">
@@ -810,7 +810,7 @@
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-028</t>
+          <t xml:space="preserve">SEC-023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -830,34 +830,34 @@
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CI workflow (lint/typecheck/build/audit)</t>
+          <t xml:space="preserve">Activate endpoint lockout</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rate-limited via Supabase (no Redis)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">.github workflow — enable Actions on GitHub</t>
+          <t xml:space="preserve">Run 2026-07-23-rate-limits.sql</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-002</t>
+          <t xml:space="preserve">SEC-024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
@@ -867,34 +867,34 @@
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Consent capture at intake</t>
+          <t xml:space="preserve">Upload token 2-min TTL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checkbox + version + timestamp (portal)</t>
+          <t xml:space="preserve">validUntil added</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Run privacy-consent migration; set Privacy Policy URL</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-004</t>
+          <t xml:space="preserve">SEC-025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="3">
@@ -904,29 +904,29 @@
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Audit log of sensitive access (=SEC-026)</t>
+          <t xml:space="preserve">backfill-shared-tasks behind admin gate</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">audit_logs + recordAudit</t>
+          <t xml:space="preserve">via middleware</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Run audit_logs migration</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-005</t>
+          <t xml:space="preserve">SEC-026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
@@ -941,34 +941,34 @@
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Right-to-be-forgotten erase endpoint</t>
+          <t xml:space="preserve">audit_logs table + recordAudit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">POST /api/admin/leads/[id]/erase (audited)</t>
+          <t xml:space="preserve">+ migration; wired impersonate/deletes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Retention schedule/purge still to define</t>
+          <t xml:space="preserve">Run 2026-07-23-audit-logs.sql</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-007</t>
+          <t xml:space="preserve">SEC-027</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="3">
@@ -978,12 +978,12 @@
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security headers (=SEC-010)</t>
+          <t xml:space="preserve">Key-rotation runbook</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See SEC-010</t>
+          <t xml:space="preserve">docs/key-rotation.md</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="2">
@@ -995,12 +995,12 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-008</t>
+          <t xml:space="preserve">SEC-028</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
@@ -1015,34 +1015,34 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PII/errors in responses+logs (=SEC-012)</t>
+          <t xml:space="preserve">CI workflow (lint/typecheck/build/audit)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See SEC-012</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">.github workflow — enable Actions on GitHub</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-003</t>
+          <t xml:space="preserve">CMP-004</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
@@ -1052,29 +1052,29 @@
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Backfill idempotency guard</t>
+          <t xml:space="preserve">Audit log of sensitive access (=SEC-026)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">migration_runs table</t>
+          <t xml:space="preserve">audit_logs + recordAudit</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Run 2026-07-23-migration-runs.sql</t>
+          <t xml:space="preserve">Run audit_logs migration</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-004</t>
+          <t xml:space="preserve">CMP-005</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
@@ -1089,29 +1089,29 @@
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shared-task mirror dedupe on retry</t>
+          <t xml:space="preserve">Right-to-be-forgotten erase endpoint</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Code-level (multi-file safe)</t>
+          <t xml:space="preserve">POST /api/admin/leads/[id]/erase (audited)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Retention schedule/purge still to define</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-005</t>
+          <t xml:space="preserve">CMP-007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Deal delete is soft delete</t>
+          <t xml:space="preserve">Security headers (=SEC-010)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No orphaned rows</t>
+          <t xml:space="preserve">See SEC-010</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="2">
@@ -1143,12 +1143,12 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-006</t>
+          <t xml:space="preserve">CMP-008</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Deal status state machine</t>
+          <t xml:space="preserve">PII/errors in responses+logs (=SEC-012)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closed is terminal</t>
+          <t xml:space="preserve">See SEC-012</t>
         </is>
       </c>
       <c r="G29" t="inlineStr" s="2">
@@ -1180,7 +1180,7 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-007</t>
+          <t xml:space="preserve">GAP-001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1200,24 +1200,24 @@
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Task status recalcs milestones</t>
+          <t xml:space="preserve">Optimistic concurrency on deal edit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Last-write-wins</t>
         </is>
       </c>
       <c r="G30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Migration + frontend conflict UI</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-008</t>
+          <t xml:space="preserve">GAP-002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
@@ -1237,24 +1237,24 @@
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compensating del() on DB-insert failure</t>
+          <t xml:space="preserve">Family-deal lookup race</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No orphan blobs; both repos</t>
+          <t xml:space="preserve">No unique index guard</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Migration + conflict handling</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-009</t>
+          <t xml:space="preserve">GAP-003</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1274,24 +1274,24 @@
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload count/size/MIME limits</t>
+          <t xml:space="preserve">Backfill idempotency guard</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25MB cap + type allow-list; both repos</t>
+          <t xml:space="preserve">migration_runs table</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Run 2026-07-23-migration-runs.sql</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-010</t>
+          <t xml:space="preserve">GAP-004</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">APS replacement side-scoped</t>
+          <t xml:space="preserve">Shared-task mirror dedupe on retry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No family-wide wipe</t>
+          <t xml:space="preserve">Code-level (multi-file safe)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
@@ -1328,7 +1328,7 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-011</t>
+          <t xml:space="preserve">GAP-005</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Welcome email idempotency</t>
+          <t xml:space="preserve">Deal delete is soft delete</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Atomic claim before send; reverts on fail</t>
+          <t xml:space="preserve">No orphaned rows</t>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="2">
@@ -1365,7 +1365,7 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-013</t>
+          <t xml:space="preserve">GAP-006</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HTML-entity brace decoding</t>
+          <t xml:space="preserve">Deal status state machine</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Decimal/hex/named in all 3 email helpers</t>
+          <t xml:space="preserve">Closed is terminal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="2">
@@ -1402,7 +1402,7 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-014</t>
+          <t xml:space="preserve">GAP-007</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Milestone-email failures logged</t>
+          <t xml:space="preserve">Task status recalcs milestones</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Thrown + non-2xx, with IDs</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G36" t="inlineStr" s="2">
@@ -1439,7 +1439,7 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-016</t>
+          <t xml:space="preserve">GAP-008</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Lead email format validation</t>
+          <t xml:space="preserve">Compensating del() on DB-insert failure</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Duplicates intentionally allowed</t>
+          <t xml:space="preserve">No orphan blobs; both repos</t>
         </is>
       </c>
       <c r="G37" t="inlineStr" s="2">
@@ -1476,7 +1476,7 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-017</t>
+          <t xml:space="preserve">GAP-009</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">file_number format on deal edit</t>
+          <t xml:space="preserve">Upload count/size/MIME limits</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Single shared regex import+edit</t>
+          <t xml:space="preserve">25MB cap + type allow-list; both repos</t>
         </is>
       </c>
       <c r="G38" t="inlineStr" s="2">
@@ -1513,7 +1513,7 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-018</t>
+          <t xml:space="preserve">GAP-010</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">field_type enum check</t>
+          <t xml:space="preserve">APS replacement side-scoped</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Allow-list on task responses</t>
+          <t xml:space="preserve">No family-wide wipe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr" s="2">
@@ -1550,7 +1550,7 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-019</t>
+          <t xml:space="preserve">GAP-011</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">APS side auto-detect legacy rows</t>
+          <t xml:space="preserve">Welcome email idempotency</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reads custom_type for side</t>
+          <t xml:space="preserve">Atomic claim before send; reverts on fail</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="2">
@@ -1587,7 +1587,7 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-020</t>
+          <t xml:space="preserve">GAP-012</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="3">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">activateClientDeals OR filter fix</t>
+          <t xml:space="preserve">Resend retry / outbox</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="2">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="G41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Needs outbox table + retry job</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-021</t>
+          <t xml:space="preserve">GAP-013</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Zero-task milestone handling</t>
+          <t xml:space="preserve">HTML-entity brace decoding</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Resolved by design (keeps manual status)</t>
+          <t xml:space="preserve">Decimal/hex/named in all 3 email helpers</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
@@ -1661,12 +1661,12 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-004</t>
+          <t xml:space="preserve">GAP-014</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Removed duplicate route stubs</t>
+          <t xml:space="preserve">Milestone-email failures logged</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Legacy URLs via next.config redirects</t>
+          <t xml:space="preserve">Thrown + non-2xx, with IDs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr" s="2">
@@ -1698,12 +1698,12 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-005</t>
+          <t xml:space="preserve">GAP-015</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Central dealMapper (toDeal)</t>
+          <t xml:space="preserve">Bulk import file validation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used by list + detail</t>
+          <t xml:space="preserve">Premise stale (CSV parsed client-side)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
@@ -1735,12 +1735,12 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-008</t>
+          <t xml:space="preserve">GAP-016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Global error boundary</t>
+          <t xml:space="preserve">Lead email format validation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">error.tsx + global-error.tsx</t>
+          <t xml:space="preserve">Duplicates intentionally allowed</t>
         </is>
       </c>
       <c r="G45" t="inlineStr" s="2">
@@ -1772,12 +1772,12 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-010</t>
+          <t xml:space="preserve">GAP-017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CLAUDE.md architecture brief</t>
+          <t xml:space="preserve">file_number format on deal edit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Authored</t>
+          <t xml:space="preserve">Single shared regex import+edit</t>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="2">
@@ -1809,12 +1809,12 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-011</t>
+          <t xml:space="preserve">GAP-018</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
@@ -1829,177 +1829,177 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Structured logger (LOG_LEVEL)</t>
+          <t xml:space="preserve">field_type enum check</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adopted in session code</t>
+          <t xml:space="preserve">Allow-list on task responses</t>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optionally set LOG_LEVEL=warn in prod</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-002</t>
+          <t xml:space="preserve">GAP-019</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">In progress</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Webhook HMAC signatures</t>
+          <t xml:space="preserve">APS side auto-detect legacy rows</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Admin verifies + portal signs; per-endpoint enforcement added</t>
+          <t xml:space="preserve">Reads custom_type for side</t>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set SERVICE_WEBHOOK_SECRET in both; then SERVICE_WEBHOOK_ENFORCE_ROUTES=activate-deal</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-003</t>
+          <t xml:space="preserve">GAP-020</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">In progress</t>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private document storage</t>
+          <t xml:space="preserve">activateClientDeals OR filter fix</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Code done both repos; dormant behind flag</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Provision private-capable Blob store, then flip NEXT_PUBLIC_PRIVATE_BLOB</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-001</t>
+          <t xml:space="preserve">GAP-021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P0</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="4">
-        <is>
-          <t xml:space="preserve">In progress</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gov IDs on public storage (=SEC-003)</t>
+          <t xml:space="preserve">Zero-task milestone handling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See SEC-003</t>
+          <t xml:space="preserve">Resolved by design (keeps manual status)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">See SEC-003</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-004</t>
+          <t xml:space="preserve">GAP-022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Gaps</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Per-deal ownership (IDOR)</t>
+          <t xml:space="preserve">Zero automated tests</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">'All admins see all' kept as intended</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Revisit if you add teams/brokers</t>
+          <t xml:space="preserve">Greenfield test-suite setup</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-007</t>
+          <t xml:space="preserve">ARC-002</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
@@ -2007,73 +2007,73 @@
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+      <c r="D52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Password-reset rate limit</t>
+          <t xml:space="preserve">Unbounded listUsers loop (N+1)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Needs shared store</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set up Upstash Redis when ready</t>
+          <t xml:space="preserve">Cache auth lookups</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-011</t>
+          <t xml:space="preserve">ARC-004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gemini per-user rate limit</t>
+          <t xml:space="preserve">Removed duplicate route stubs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Needs shared store</t>
+          <t xml:space="preserve">Legacy URLs via next.config redirects</t>
         </is>
       </c>
       <c r="G53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set up Upstash Redis when ready</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-015</t>
+          <t xml:space="preserve">ARC-005</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
@@ -2081,36 +2081,36 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+      <c r="D54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">daisyUI v3 outdated</t>
+          <t xml:space="preserve">Central dealMapper (toDeal)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Major upgrade, visual-regression risk</t>
+          <t xml:space="preserve">Used by list + detail</t>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approve + QA later</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-018</t>
+          <t xml:space="preserve">ARC-008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
@@ -2118,36 +2118,36 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+      <c r="D55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Align Tailwind 3/4</t>
+          <t xml:space="preserve">Global error boundary</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Major dep change</t>
+          <t xml:space="preserve">error.tsx + global-error.tsx</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approve + QA later</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-021</t>
+          <t xml:space="preserve">ARC-010</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
@@ -2155,36 +2155,36 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+      <c r="D56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Virus-scan uploads</t>
+          <t xml:space="preserve">CLAUDE.md architecture brief</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reduced by GAP-009 type limits</t>
+          <t xml:space="preserve">Authored</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pick a scanning service</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SEC-023</t>
+          <t xml:space="preserve">ARC-011</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Security</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
@@ -2192,105 +2192,105 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+      <c r="D57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Activate endpoint lockout</t>
+          <t xml:space="preserve">Structured logger (LOG_LEVEL)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Needs shared store</t>
+          <t xml:space="preserve">Adopted in session code</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set up Upstash Redis when ready</t>
+          <t xml:space="preserve">Optionally set LOG_LEVEL=warn in prod</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-006</t>
+          <t xml:space="preserve">ARC-012</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CASL unsubscribe + postal address</t>
+          <t xml:space="preserve">Test/release gate in CI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Emails lack unsubscribe</t>
+          <t xml:space="preserve">Largely covered by SEC-028 CI; tests=GAP-022</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Give me iClosed mailing address</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-007</t>
+          <t xml:space="preserve">SEC-003</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">Deferred</t>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">In progress</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mixed Tailwind 3+4</t>
+          <t xml:space="preserve">Private document storage</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tied to SEC-018</t>
+          <t xml:space="preserve">Code done both repos; dormant behind flag</t>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Approve + QA later</t>
+          <t xml:space="preserve">Provision private-capable Blob store, then flip NEXT_PUBLIC_PRIVATE_BLOB</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CMP-003</t>
+          <t xml:space="preserve">CMP-001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2303,73 +2303,73 @@
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+      <c r="D60" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">In progress</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gemini sub-processor DPA/disclosure</t>
+          <t xml:space="preserve">Gov IDs on public storage (=SEC-003)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Legal + code</t>
+          <t xml:space="preserve">See SEC-003</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sign DPA / disclose in privacy policy</t>
+          <t xml:space="preserve">See SEC-003</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-001</t>
+          <t xml:space="preserve">SEC-015</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">Deferred</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optimistic concurrency on deal edit</t>
+          <t xml:space="preserve">daisyUI v3 outdated</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Last-write-wins</t>
+          <t xml:space="preserve">Major upgrade, visual-regression risk</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Migration + frontend conflict UI</t>
+          <t xml:space="preserve">Approve + QA later</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-002</t>
+          <t xml:space="preserve">SEC-018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
@@ -2377,36 +2377,36 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+      <c r="D62" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">Deferred</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Family-deal lookup race</t>
+          <t xml:space="preserve">Align Tailwind 3/4</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No unique index guard</t>
+          <t xml:space="preserve">Major dep change</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Migration + conflict handling</t>
+          <t xml:space="preserve">Approve + QA later</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-012</t>
+          <t xml:space="preserve">SEC-021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Security</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
@@ -2414,73 +2414,73 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+      <c r="D63" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">Deferred</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Resend retry / outbox</t>
+          <t xml:space="preserve">Virus-scan uploads</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Reduced by GAP-009 type limits</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Needs outbox table + retry job</t>
+          <t xml:space="preserve">Pick a scanning service</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-015</t>
+          <t xml:space="preserve">CMP-006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">Deferred</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Bulk import file validation</t>
+          <t xml:space="preserve">CASL unsubscribe + postal address</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Premise stale (CSV parsed client-side)</t>
+          <t xml:space="preserve">Emails lack unsubscribe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Give me iClosed mailing address</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GAP-022</t>
+          <t xml:space="preserve">ARC-007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gaps</t>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
@@ -2488,41 +2488,41 @@
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">Not started</t>
+      <c r="D65" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">Deferred</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Zero automated tests</t>
+          <t xml:space="preserve">Mixed Tailwind 3+4</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Tied to SEC-018</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Greenfield test-suite setup</t>
+          <t xml:space="preserve">Approve + QA later</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-001</t>
+          <t xml:space="preserve">CMP-002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="5">
@@ -2532,34 +2532,34 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pagination on /api/admin/deals</t>
+          <t xml:space="preserve">Consent capture at intake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole table returned</t>
+          <t xml:space="preserve">Removed at user request (reverted)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Frontend + API</t>
+          <t xml:space="preserve">Run privacy-consent migration; set Privacy Policy URL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-002</t>
+          <t xml:space="preserve">CMP-003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Architecture</t>
+          <t xml:space="preserve">Compliance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P1</t>
+          <t xml:space="preserve">P0</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="5">
@@ -2569,24 +2569,24 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Unbounded listUsers loop (N+1)</t>
+          <t xml:space="preserve">Gemini sub-processor DPA/disclosure</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Legal + code</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cache auth lookups</t>
+          <t xml:space="preserve">Sign DPA / disclose in privacy policy</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-003</t>
+          <t xml:space="preserve">ARC-001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P2</t>
+          <t xml:space="preserve">P1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="5">
@@ -2606,24 +2606,24 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DealList virtualization</t>
+          <t xml:space="preserve">Pagination on /api/admin/deals</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Needs pagination first</t>
+          <t xml:space="preserve">Whole table returned</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Frontend + API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-006</t>
+          <t xml:space="preserve">ARC-003</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2643,24 +2643,24 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Pervasive any types</t>
+          <t xml:space="preserve">DealList virtualization</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Needs pagination first</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Repo-wide sweep</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-009</t>
+          <t xml:space="preserve">ARC-006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Consistent API error shape</t>
+          <t xml:space="preserve">Pervasive any types</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="2">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="G70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">~84-route sweep (decision)</t>
+          <t xml:space="preserve">Repo-wide sweep</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ARC-012</t>
+          <t xml:space="preserve">ARC-009</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Test/release gate in CI</t>
+          <t xml:space="preserve">Consistent API error shape</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Largely covered by SEC-028 CI; tests=GAP-022</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">~84-route sweep (decision)</t>
         </is>
       </c>
     </row>
